--- a/app/test-data/排课结果_2026年010月.xlsx
+++ b/app/test-data/排课结果_2026年010月.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E131"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -425,220 +425,220 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>27全程1期,27全程2期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B2" t="str">
-        <v>高数1-函数、极限、连续1</v>
+        <v>计算机1</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-02</v>
       </c>
       <c r="D2" t="str">
-        <v>19:00 - 20:50</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E2" t="str">
-        <v>王喆</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>27OMO2期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B3" t="str">
-        <v>高数-选填题技巧与方法（一）</v>
+        <v>日语1</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-10-03</v>
+        <v>2026-10-02</v>
       </c>
       <c r="D3" t="str">
-        <v>18:00 - 20:00</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E3" t="str">
-        <v>窦峥</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B4" t="str">
-        <v>线代-行列式与矩阵的重要性质</v>
+        <v>计算机1-1</v>
       </c>
       <c r="C4" t="str">
         <v>2026-10-03</v>
       </c>
       <c r="D4" t="str">
-        <v>20:30 - 22:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E4" t="str">
-        <v>方浩</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>28早鸟1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B5" t="str">
-        <v>高数5-函数极限的计算2</v>
+        <v>日语1-1</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-03</v>
       </c>
       <c r="D5" t="str">
-        <v>17:00 - 18:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E5" t="str">
-        <v>王喆</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>27全程1期,27全程2期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B6" t="str">
-        <v>高数2-函数、极限、连续2</v>
+        <v>秋季阶段测讲评</v>
       </c>
       <c r="C6" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="D6" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 20:00</v>
       </c>
       <c r="E6" t="str">
-        <v>王喆</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>28OMO1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B7" t="str">
-        <v>高数1-函数</v>
+        <v>计算机2</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="D7" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:40</v>
       </c>
       <c r="E7" t="str">
-        <v>窦峥</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>27OMO2期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B8" t="str">
-        <v>高数-选填题技巧与方法（二）</v>
+        <v>日语2</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-10-06</v>
+        <v>2026-10-04</v>
       </c>
       <c r="D8" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:40</v>
       </c>
       <c r="E8" t="str">
-        <v>窦峥</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>27全程1期,27全程2期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期</v>
       </c>
       <c r="B9" t="str">
-        <v>高数3-一元微分学1</v>
+        <v>线代3-矩阵及其运算</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="D9" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E9" t="str">
-        <v>王喆</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>27OMO1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B10" t="str">
-        <v>高数-解答题题型与方法（一）</v>
+        <v>计算机3</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-06</v>
       </c>
       <c r="D10" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:15</v>
       </c>
       <c r="E10" t="str">
-        <v>窦峥</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>28早鸟4期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B11" t="str">
-        <v>线代1-行列式的概念及性质</v>
+        <v>日语3</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-06</v>
       </c>
       <c r="D11" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 20:15</v>
       </c>
       <c r="E11" t="str">
-        <v>李良</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B12" t="str">
-        <v>线代-矩阵的初等变换与秩</v>
+        <v>线代1-行列式与矩阵</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="D12" t="str">
-        <v>20:30 - 22:30</v>
+        <v>16:30 - 18:20</v>
       </c>
       <c r="E12" t="str">
-        <v>方浩</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>27全程1期,27全程2期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B13" t="str">
-        <v>高数4-一元微分学2</v>
+        <v>找雷秘笈专题串讲3</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="D13" t="str">
-        <v>19:00 - 20:50</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E13" t="str">
-        <v>王喆</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>28早鸟1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B14" t="str">
-        <v>高数6-数列极限的计算</v>
+        <v>高数1-函数及其四个特性</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-07</v>
       </c>
       <c r="D14" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E14" t="str">
         <v>王喆</v>
@@ -646,16 +646,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>27OMO2期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B15" t="str">
-        <v>高数-选填题技巧与方法（三）</v>
+        <v>高数4-极限计算1</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-07</v>
       </c>
       <c r="D15" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E15" t="str">
         <v>窦峥</v>
@@ -663,302 +663,302 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>27全程2期</v>
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B16" t="str">
-        <v>高数5-一元积分学1</v>
+        <v>线代-相似的应用</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-10-11</v>
+        <v>2026-10-07</v>
       </c>
       <c r="D16" t="str">
-        <v>17:30 - 18:50</v>
+        <v>20:00 - 22:00</v>
       </c>
       <c r="E16" t="str">
-        <v>王喆</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>27全程1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B17" t="str">
-        <v>高数5-一元积分学1</v>
+        <v>计算机4</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-10-11</v>
+        <v>2026-10-08</v>
       </c>
       <c r="D17" t="str">
-        <v>19:00 - 20:20</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E17" t="str">
-        <v>王喆</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>27全程1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B18" t="str">
-        <v>高数6-一元积分学2</v>
+        <v>日语4</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-10-14</v>
+        <v>2026-10-08</v>
       </c>
       <c r="D18" t="str">
-        <v>19:00 - 20:20</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E18" t="str">
-        <v>王喆</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>27OMO2期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
       </c>
       <c r="B19" t="str">
-        <v>高数-解答题题型与方法（一）</v>
+        <v>计算机10</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-10-14</v>
+        <v>2026-10-08</v>
       </c>
       <c r="D19" t="str">
-        <v>19:00 - 21:30</v>
+        <v>21:00 - 22:20</v>
       </c>
       <c r="E19" t="str">
-        <v>窦峥</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>28早鸟1期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
       </c>
       <c r="B20" t="str">
-        <v>高数7-函数的连续性与间断点</v>
+        <v>日语10</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-08</v>
       </c>
       <c r="D20" t="str">
-        <v>19:00 - 20:30</v>
+        <v>21:00 - 22:20</v>
       </c>
       <c r="E20" t="str">
-        <v>王喆</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>28OMO1期</v>
+        <v>27名师</v>
       </c>
       <c r="B21" t="str">
-        <v>高数2-极限存在的定义与性质</v>
+        <v>马原选择题1</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D21" t="str">
-        <v>19:00 - 21:30</v>
+        <v>17:00 - 19:00</v>
       </c>
       <c r="E21" t="str">
-        <v>窦峥</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B22" t="str">
-        <v>线代-向量组重点题型</v>
+        <v>线代2-向量</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D22" t="str">
-        <v>20:30 - 22:30</v>
+        <v>17:00 - 18:30</v>
       </c>
       <c r="E22" t="str">
-        <v>方浩</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27OMO1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B23" t="str">
-        <v>高数-解答题题型与方法（二）</v>
+        <v>高数2-极限的定义与性质</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-10-16</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D23" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:40</v>
       </c>
       <c r="E23" t="str">
-        <v>窦峥</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>27全程2期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B24" t="str">
-        <v>高数6-一元积分学2</v>
+        <v>线代1-行列式的概念与性质</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D24" t="str">
-        <v>17:30 - 18:50</v>
+        <v>20:00 - 22:20</v>
       </c>
       <c r="E24" t="str">
-        <v>王喆</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>27全程1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B25" t="str">
-        <v>高数7-常微分方程</v>
+        <v>计算机1-2</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D25" t="str">
-        <v>19:00 - 20:30</v>
+        <v>21:00 - 22:30</v>
       </c>
       <c r="E25" t="str">
-        <v>王喆</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B26" t="str">
-        <v>线代-方程组重点题型</v>
+        <v>日语1-2</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-09</v>
       </c>
       <c r="D26" t="str">
-        <v>20:30 - 22:30</v>
+        <v>21:00 - 22:30</v>
       </c>
       <c r="E26" t="str">
-        <v>方浩</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>27全程1期</v>
+        <v>27全程培优</v>
       </c>
       <c r="B27" t="str">
-        <v>高数8-多元函数微分学</v>
+        <v>选择题重难点突破1</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-10-18</v>
+        <v>2026-10-10</v>
       </c>
       <c r="D27" t="str">
-        <v>19:00 - 21:20</v>
+        <v>17:00 - 19:00</v>
       </c>
       <c r="E27" t="str">
-        <v>王喆</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>27OMO2期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B28" t="str">
-        <v>高数-解答题题型与方法（二）</v>
+        <v>史纲预热串讲8</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-10-18</v>
+        <v>2026-10-10</v>
       </c>
       <c r="D28" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E28" t="str">
-        <v>窦峥</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28早鸟1期</v>
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B29" t="str">
-        <v>线代1-行列式定义与性质</v>
+        <v>线代-二次型重点题型</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-10-20</v>
+        <v>2026-10-10</v>
       </c>
       <c r="D29" t="str">
-        <v>19:00 - 20:30</v>
+        <v>20:00 - 22:00</v>
       </c>
       <c r="E29" t="str">
-        <v>窦峥</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>28早鸟1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B30" t="str">
-        <v>高数8-导数与微分的定义</v>
+        <v>计算机5</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-11</v>
       </c>
       <c r="D30" t="str">
-        <v>19:00 - 20:30</v>
+        <v>17:00 - 18:30</v>
       </c>
       <c r="E30" t="str">
-        <v>王喆</v>
+        <v>乔石磊</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>27OMO1期,27OMO2期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B31" t="str">
-        <v>高数-证明题分析思路与证明方法（一）</v>
+        <v>日语5</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-11</v>
       </c>
       <c r="D31" t="str">
-        <v>19:00 - 21:30</v>
+        <v>17:00 - 18:30</v>
       </c>
       <c r="E31" t="str">
-        <v>窦峥</v>
+        <v>aki</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>27全程1期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B32" t="str">
-        <v>高数-证明题分析思路与证明方法（一）</v>
+        <v>找雷秘笈专题串讲4</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-11</v>
       </c>
       <c r="D32" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E32" t="str">
-        <v>王喆</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>28早鸟4期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B33" t="str">
-        <v>线代2-行列式的展开定理与克拉默法则</v>
+        <v>线代1-行列式的概念及性质</v>
       </c>
       <c r="C33" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-11</v>
       </c>
       <c r="D33" t="str">
         <v>19:00 - 20:30</v>
@@ -972,13 +972,13 @@
         <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B34" t="str">
-        <v>线代-相似的判定与性质</v>
+        <v>概率-随机事件与概率</v>
       </c>
       <c r="C34" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-11</v>
       </c>
       <c r="D34" t="str">
-        <v>20:30 - 22:30</v>
+        <v>20:00 - 22:00</v>
       </c>
       <c r="E34" t="str">
         <v>方浩</v>
@@ -986,16 +986,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>27全程2期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
       </c>
       <c r="B35" t="str">
-        <v>高数7-常微分方程</v>
+        <v>高数10-中值定理1</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D35" t="str">
-        <v>19:00 - 20:30</v>
+        <v>14:40 - 16:00</v>
       </c>
       <c r="E35" t="str">
         <v>王喆</v>
@@ -1003,160 +1003,1639 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>28OMO1期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B36" t="str">
-        <v>高数3-无穷小与无穷大量</v>
+        <v>线代3-方程组</v>
       </c>
       <c r="C36" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D36" t="str">
-        <v>17:30 - 18:30</v>
+        <v>16:30 - 18:30</v>
       </c>
       <c r="E36" t="str">
-        <v>窦峥</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>27全程1期</v>
+        <v>27名师</v>
       </c>
       <c r="B37" t="str">
-        <v>高数-证明题分析思路与证明方法（二）</v>
+        <v>马原选择题2</v>
       </c>
       <c r="C37" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D37" t="str">
-        <v>19:00 - 21:30</v>
+        <v>17:00 - 19:00</v>
       </c>
       <c r="E37" t="str">
-        <v>王喆</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>27OMO1期,27OMO2期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B38" t="str">
-        <v>高数-证明题分析思路与证明方法（二）</v>
+        <v>史纲预热11</v>
       </c>
       <c r="C38" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D38" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E38" t="str">
-        <v>窦峥</v>
+        <v>孔昱力</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>28早鸟1期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B39" t="str">
-        <v>线代2-行列式的计算与克莱默法则</v>
+        <v>高数3-无穷小、无穷大及其阶</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D39" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 20:15</v>
       </c>
       <c r="E39" t="str">
-        <v>窦峥</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>28早鸟1期</v>
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B40" t="str">
-        <v>高数9-导数的计算</v>
+        <v>概率-分布函数重点题型1</v>
       </c>
       <c r="C40" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-12</v>
       </c>
       <c r="D40" t="str">
-        <v>17:00 - 18:30</v>
+        <v>20:00 - 22:00</v>
       </c>
       <c r="E40" t="str">
-        <v>王喆</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>27全程1期</v>
+        <v>27全程培优</v>
       </c>
       <c r="B41" t="str">
-        <v>高数-专项部分题型与方法</v>
+        <v>选择题重难点突破2</v>
       </c>
       <c r="C41" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-13</v>
       </c>
       <c r="D41" t="str">
-        <v>19:00 - 21:30</v>
+        <v>17:00 - 19:00</v>
       </c>
       <c r="E41" t="str">
-        <v>王喆</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>27OMO1期,27OMO2期</v>
+        <v>28全程2期</v>
       </c>
       <c r="B42" t="str">
-        <v>高数-专项部分题型与方法</v>
+        <v>高数4-函数极限的计算1</v>
       </c>
       <c r="C42" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-13</v>
       </c>
       <c r="D42" t="str">
-        <v>19:00 - 21:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E42" t="str">
-        <v>窦峥</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>27全程2期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期</v>
       </c>
       <c r="B43" t="str">
-        <v>高数8-多元函数微分学</v>
+        <v>线代4-矩阵的逆</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-13</v>
       </c>
       <c r="D43" t="str">
-        <v>19:00 - 21:20</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E43" t="str">
-        <v>王喆</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B44" t="str">
+        <v>线代4-特征值与特征向量</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D44" t="str">
+        <v>16:30 - 18:30</v>
+      </c>
+      <c r="E44" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B45" t="str">
+        <v>高数5-函数极限的计算2</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D45" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E45" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B46" t="str">
+        <v>高数5-极限计算2</v>
+      </c>
+      <c r="C46" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D46" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E46" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
         <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
-      <c r="B44" t="str">
-        <v>线代-相似的应用</v>
-      </c>
-      <c r="C44" t="str">
+      <c r="B47" t="str">
+        <v>概率-分布函数重点题型2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D47" t="str">
+        <v>20:00 - 22:00</v>
+      </c>
+      <c r="E47" t="str">
+        <v>方浩</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B48" t="str">
+        <v>计算机6</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D48" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E48" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B49" t="str">
+        <v>日语6</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="D49" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E49" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>27名师</v>
+      </c>
+      <c r="B50" t="str">
+        <v>马原选择题3</v>
+      </c>
+      <c r="C50" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="D50" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E50" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B51" t="str">
+        <v>主观题分必分技巧1</v>
+      </c>
+      <c r="C51" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="D51" t="str">
+        <v>19:00 - 22:00</v>
+      </c>
+      <c r="E51" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B52" t="str">
+        <v>线代2-行列式的展开定理与克拉默法则</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="D52" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E52" t="str">
+        <v>李良</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B53" t="str">
+        <v>计算机1-3</v>
+      </c>
+      <c r="C53" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="D53" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E53" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B54" t="str">
+        <v>日语1-3</v>
+      </c>
+      <c r="C54" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="D54" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E54" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>27全程培优</v>
+      </c>
+      <c r="B55" t="str">
+        <v>选择题重难点突破3</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D55" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E55" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B56" t="str">
+        <v>高数6-数列极限的计算</v>
+      </c>
+      <c r="C56" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D56" t="str">
+        <v>17:00 - 18:30</v>
+      </c>
+      <c r="E56" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B57" t="str">
+        <v>史纲预热串讲9</v>
+      </c>
+      <c r="C57" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D57" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E57" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B58" t="str">
+        <v>线代5-二次型</v>
+      </c>
+      <c r="C58" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D58" t="str">
+        <v>19:30 - 21:00</v>
+      </c>
+      <c r="E58" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B59" t="str">
+        <v>计算机7</v>
+      </c>
+      <c r="C59" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D59" t="str">
+        <v>21:30 - 23:00</v>
+      </c>
+      <c r="E59" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B60" t="str">
+        <v>日语7</v>
+      </c>
+      <c r="C60" t="str">
+        <v>2026-10-16</v>
+      </c>
+      <c r="D60" t="str">
+        <v>21:30 - 23:00</v>
+      </c>
+      <c r="E60" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B61" t="str">
+        <v>火星姐姐背诵手册冲刺串讲1</v>
+      </c>
+      <c r="C61" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="D61" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E61" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B62" t="str">
+        <v>史纲预热12</v>
+      </c>
+      <c r="C62" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="D62" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E62" t="str">
+        <v>孔昱力</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B63" t="str">
+        <v>计算机11</v>
+      </c>
+      <c r="C63" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="D63" t="str">
+        <v>19:00 - 20:10</v>
+      </c>
+      <c r="E63" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B64" t="str">
+        <v>日语11</v>
+      </c>
+      <c r="C64" t="str">
+        <v>2026-10-17</v>
+      </c>
+      <c r="D64" t="str">
+        <v>19:00 - 20:10</v>
+      </c>
+      <c r="E64" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>27名师</v>
+      </c>
+      <c r="B65" t="str">
+        <v>史纲＆毛特选择题1</v>
+      </c>
+      <c r="C65" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D65" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E65" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B66" t="str">
+        <v>计算机1-3</v>
+      </c>
+      <c r="C66" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D66" t="str">
+        <v>17:00 - 18:30</v>
+      </c>
+      <c r="E66" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B67" t="str">
+        <v>日语1-3</v>
+      </c>
+      <c r="C67" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D67" t="str">
+        <v>17:00 - 18:30</v>
+      </c>
+      <c r="E67" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B68" t="str">
+        <v>线代3-矩阵的概念与运算</v>
+      </c>
+      <c r="C68" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D68" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E68" t="str">
+        <v>李良</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B69" t="str">
+        <v>计算机8</v>
+      </c>
+      <c r="C69" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D69" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E69" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B70" t="str">
+        <v>日语8</v>
+      </c>
+      <c r="C70" t="str">
+        <v>2026-10-18</v>
+      </c>
+      <c r="D70" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E70" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B71" t="str">
+        <v>概率1-随机事件与一维随机变量</v>
+      </c>
+      <c r="C71" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="D71" t="str">
+        <v>14:30 - 16:10</v>
+      </c>
+      <c r="E71" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>27全程培优</v>
+      </c>
+      <c r="B72" t="str">
+        <v>选择题重难点突破4</v>
+      </c>
+      <c r="C72" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="D72" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E72" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B73" t="str">
+        <v>线代3-矩阵的概念与运算</v>
+      </c>
+      <c r="C73" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="D73" t="str">
+        <v>17:00 - 18:30</v>
+      </c>
+      <c r="E73" t="str">
+        <v>李良</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B74" t="str">
+        <v>高数7-函数的连续性与间断点</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="D74" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E74" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B75" t="str">
+        <v>概率-数字特征</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="D75" t="str">
+        <v>20:00 - 22:00</v>
+      </c>
+      <c r="E75" t="str">
+        <v>方浩</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B76" t="str">
+        <v>高数11-中值定理2</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D76" t="str">
+        <v>17:00 - 18:10</v>
+      </c>
+      <c r="E76" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B77" t="str">
+        <v>火星姐姐背诵手册冲刺串讲2</v>
+      </c>
+      <c r="C77" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D77" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E77" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B78" t="str">
+        <v>高数8-导数与微分的定义</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D78" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E78" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期</v>
+      </c>
+      <c r="B79" t="str">
+        <v>线代5-分块矩阵</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D79" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E79" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B80" t="str">
+        <v>计算机1-4</v>
+      </c>
+      <c r="C80" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D80" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E80" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B81" t="str">
+        <v>日语1-4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2026-10-20</v>
+      </c>
+      <c r="D81" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E81" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>27名师</v>
+      </c>
+      <c r="B82" t="str">
+        <v>史纲＆毛特选择题2</v>
+      </c>
+      <c r="C82" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D82" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E82" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B83" t="str">
+        <v>主观题分必分技巧2</v>
+      </c>
+      <c r="C83" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D83" t="str">
+        <v>19:00 - 22:00</v>
+      </c>
+      <c r="E83" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B84" t="str">
+        <v>高数9-导数的计算</v>
+      </c>
+      <c r="C84" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D84" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E84" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B85" t="str">
+        <v>高数6-极限计算3</v>
+      </c>
+      <c r="C85" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D85" t="str">
+        <v>19:00 - 21:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B86" t="str">
+        <v>概率-大数定律与数理统计基本理论</v>
+      </c>
+      <c r="C86" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D86" t="str">
+        <v>20:00 - 22:00</v>
+      </c>
+      <c r="E86" t="str">
+        <v>方浩</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B87" t="str">
+        <v>计算机9</v>
+      </c>
+      <c r="C87" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D87" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E87" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B88" t="str">
+        <v>日语9</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2026-10-21</v>
+      </c>
+      <c r="D88" t="str">
+        <v>21:00 - 22:30</v>
+      </c>
+      <c r="E88" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B89" t="str">
+        <v>火星姐姐背诵手册冲刺串讲3</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="D89" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E89" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B90" t="str">
+        <v>史纲预热串讲10</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="D90" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E90" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B91" t="str">
+        <v>史纲预热13</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="D91" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E91" t="str">
+        <v>孔昱力</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B92" t="str">
+        <v>概率2-二维随机变量及其分布</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="D92" t="str">
+        <v>19:30 - 21:30</v>
+      </c>
+      <c r="E92" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B93" t="str">
+        <v>概率3-数字特征</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D93" t="str">
+        <v>14:30 - 16:00</v>
+      </c>
+      <c r="E93" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>27全程培优</v>
+      </c>
+      <c r="B94" t="str">
+        <v>选择题重难点突破5</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D94" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E94" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B95" t="str">
+        <v>高数10-中值定理1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D95" t="str">
+        <v>19:00 - 20:20</v>
+      </c>
+      <c r="E95" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B96" t="str">
+        <v>计算机10</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D96" t="str">
+        <v>20:30 - 21:50</v>
+      </c>
+      <c r="E96" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B97" t="str">
+        <v>日语10</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="D97" t="str">
+        <v>20:30 - 21:50</v>
+      </c>
+      <c r="E97" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B98" t="str">
+        <v>火星姐姐背诵手册冲刺串讲4</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="D98" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E98" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B99" t="str">
+        <v>线代4-伴随矩阵与矩阵的逆</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="D99" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E99" t="str">
+        <v>李良</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>27名师</v>
+      </c>
+      <c r="B100" t="str">
+        <v>史纲＆毛特选择题3</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="D100" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="E100" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>27全程培优</v>
+      </c>
+      <c r="B101" t="str">
+        <v>选择题重难点突破6</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="D101" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E101" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B102" t="str">
+        <v>计算机11</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="D102" t="str">
+        <v>19:00 - 20:10</v>
+      </c>
+      <c r="E102" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B103" t="str">
+        <v>日语11</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2026-10-25</v>
+      </c>
+      <c r="D103" t="str">
+        <v>19:00 - 20:10</v>
+      </c>
+      <c r="E103" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B104" t="str">
+        <v>火星姐姐背诵手册冲刺串讲5</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="D104" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E104" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B105" t="str">
+        <v>高数11-中值定理2</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="D105" t="str">
+        <v>19:00 - 20:10</v>
+      </c>
+      <c r="E105" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B106" t="str">
+        <v>概率-点估计</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="D106" t="str">
+        <v>20:00 - 22:00</v>
+      </c>
+      <c r="E106" t="str">
+        <v>方浩</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B107" t="str">
+        <v>计算机12</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="D107" t="str">
+        <v>20:30 - 22:10</v>
+      </c>
+      <c r="E107" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B108" t="str">
+        <v>日语12</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="D108" t="str">
+        <v>20:30 - 22:10</v>
+      </c>
+      <c r="E108" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期</v>
+      </c>
+      <c r="B109" t="str">
+        <v>线代6-初等变换与初等矩阵</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D109" t="str">
+        <v>17:00 - 18:30</v>
+      </c>
+      <c r="E109" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B110" t="str">
+        <v>计算机1-5</v>
+      </c>
+      <c r="C110" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D110" t="str">
+        <v>18:00 - 18:40</v>
+      </c>
+      <c r="E110" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B111" t="str">
+        <v>日语1-5</v>
+      </c>
+      <c r="C111" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D111" t="str">
+        <v>18:00 - 18:40</v>
+      </c>
+      <c r="E111" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B112" t="str">
+        <v>史纲预热串讲11</v>
+      </c>
+      <c r="C112" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D112" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E112" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B113" t="str">
+        <v>史纲预热14</v>
+      </c>
+      <c r="C113" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D113" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E113" t="str">
+        <v>孔昱力</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B114" t="str">
+        <v>概率4-数理统计与参数估计</v>
+      </c>
+      <c r="C114" t="str">
+        <v>2026-10-27</v>
+      </c>
+      <c r="D114" t="str">
+        <v>19:00 - 20:30</v>
+      </c>
+      <c r="E114" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期</v>
+      </c>
+      <c r="B115" t="str">
+        <v>高数12-中值定理3</v>
+      </c>
+      <c r="C115" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D115" t="str">
+        <v>16:30 - 18:10</v>
+      </c>
+      <c r="E115" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>27全程培优</v>
+      </c>
+      <c r="B116" t="str">
+        <v>选择题重难点突破7</v>
+      </c>
+      <c r="C116" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D116" t="str">
+        <v>17:00 - 19:00</v>
+      </c>
+      <c r="E116" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B117" t="str">
+        <v>高数12-中值定理3</v>
+      </c>
+      <c r="C117" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D117" t="str">
+        <v>19:00 - 20:40</v>
+      </c>
+      <c r="E117" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B118" t="str">
+        <v>高数7-极限存在准则</v>
+      </c>
+      <c r="C118" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D118" t="str">
+        <v>19:00 - 20:00</v>
+      </c>
+      <c r="E118" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B119" t="str">
+        <v>分析题考点冲刺串讲1</v>
+      </c>
+      <c r="C119" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D119" t="str">
+        <v>19:30 - 21:30</v>
+      </c>
+      <c r="E119" t="str">
+        <v>石磊</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B120" t="str">
+        <v>概率-数一专题</v>
+      </c>
+      <c r="C120" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D120" t="str">
+        <v>20:00 - 22:00</v>
+      </c>
+      <c r="E120" t="str">
+        <v>方浩</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B121" t="str">
+        <v>计算机12</v>
+      </c>
+      <c r="C121" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D121" t="str">
+        <v>21:00 - 22:40</v>
+      </c>
+      <c r="E121" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>28全程2期</v>
+      </c>
+      <c r="B122" t="str">
+        <v>日语12</v>
+      </c>
+      <c r="C122" t="str">
+        <v>2026-10-28</v>
+      </c>
+      <c r="D122" t="str">
+        <v>21:00 - 22:40</v>
+      </c>
+      <c r="E122" t="str">
+        <v>aki</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+      </c>
+      <c r="B123" t="str">
+        <v>专项阶段测试讲评</v>
+      </c>
+      <c r="C123" t="str">
         <v>2026-10-29</v>
       </c>
-      <c r="D44" t="str">
-        <v>20:30 - 22:30</v>
-      </c>
-      <c r="E44" t="str">
+      <c r="D123" t="str">
+        <v>14:00 - 16:00</v>
+      </c>
+      <c r="E123" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>27名师</v>
+      </c>
+      <c r="B124" t="str">
+        <v>主讲小灶：测试复盘</v>
+      </c>
+      <c r="C124" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="D124" t="str">
+        <v>16:00 - 17:00</v>
+      </c>
+      <c r="E124" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B125" t="str">
+        <v>火星姐姐背诵手册冲刺串讲6</v>
+      </c>
+      <c r="C125" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="D125" t="str">
+        <v>17:30 - 19:00</v>
+      </c>
+      <c r="E125" t="str">
+        <v>火星姐姐</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+      </c>
+      <c r="B126" t="str">
+        <v>线代5-分块矩阵</v>
+      </c>
+      <c r="C126" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="D126" t="str">
+        <v>18:00 - 18:40</v>
+      </c>
+      <c r="E126" t="str">
+        <v>李良</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B127" t="str">
+        <v>高数13-导数应用1</v>
+      </c>
+      <c r="C127" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="D127" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E127" t="str">
+        <v>王喆</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+      </c>
+      <c r="B128" t="str">
+        <v>线代2-行列式展开定理与克拉默法则</v>
+      </c>
+      <c r="C128" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="D128" t="str">
+        <v>20:00 - 21:30</v>
+      </c>
+      <c r="E128" t="str">
         <v>方浩</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+      </c>
+      <c r="B129" t="str">
+        <v>专项阶段测试讲评</v>
+      </c>
+      <c r="C129" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="D129" t="str">
+        <v>19:00 - 22:00</v>
+      </c>
+      <c r="E129" t="str">
+        <v>窦峥</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B130" t="str">
+        <v>计算机13</v>
+      </c>
+      <c r="C130" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="D130" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E130" t="str">
+        <v>乔石磊</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+      </c>
+      <c r="B131" t="str">
+        <v>日语13</v>
+      </c>
+      <c r="C131" t="str">
+        <v>2026-10-30</v>
+      </c>
+      <c r="D131" t="str">
+        <v>19:00 - 21:00</v>
+      </c>
+      <c r="E131" t="str">
+        <v>aki</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E131"/>
   </ignoredErrors>
 </worksheet>
 </file>